--- a/evaluation/file-processing-fixtures/long-table-expenses.xlsx
+++ b/evaluation/file-processing-fixtures/long-table-expenses.xlsx
@@ -1,3 +1,11 @@
+
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheets>
+    <sheet name="経費" sheetId="1" r:id="rId1"/>
+  </sheets>
+</workbook>
+</file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -197,6 +205,31 @@
     <t>3000円</t>
   </si>
 </sst>
+</file>
+
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="1">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+  </fonts>
+  <fills count="1">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border/>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  </cellXfs>
+</styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
